--- a/ECON251/Assignment/Group assignment data sheet.xlsx
+++ b/ECON251/Assignment/Group assignment data sheet.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ECON251\Assignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7759A96A-F005-4CDC-A6D3-5BC0A0A2F03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B7E99B-9CC9-4638-A68C-C9E00603FF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INDIA_RAW_DATA" sheetId="1" r:id="rId1"/>
-    <sheet name="host country" sheetId="2" r:id="rId2"/>
+    <sheet name="host country (india)" sheetId="2" r:id="rId2"/>
     <sheet name="host - china" sheetId="3" r:id="rId3"/>
     <sheet name="host-topFDI" sheetId="4" r:id="rId4"/>
     <sheet name="Charts" sheetId="5" r:id="rId5"/>
@@ -766,36 +766,74 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr sz="1400" b="0" i="0">
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>CHART-1:Structural Transformation of Employment By Sector in (India)</a:t>
+              <a:t>Chart 1: Structural Transformation of Employment By Sector in (India)</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -803,104 +841,132 @@
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="percentStacked"/>
-        <c:varyColors val="1"/>
+        <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Employment in agriculture</c:v>
+            <c:v>Employment in Agriculture</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="156082"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
-            <a:ln cmpd="sng">
+            <a:ln>
               <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="1"/>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'host country'!$B$27:$B$52</c:f>
+              <c:f>'host country (india)'!$B$18:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="10">
                   <c:v>2001</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>2002</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="12">
                   <c:v>2003</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="13">
                   <c:v>2004</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="14">
                   <c:v>2005</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="15">
                   <c:v>2006</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="16">
                   <c:v>2007</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="17">
                   <c:v>2008</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="18">
                   <c:v>2009</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="20">
                   <c:v>2011</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="21">
                   <c:v>2012</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="22">
                   <c:v>2013</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="23">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="24">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="25">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="26">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="27">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="28">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="29">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="30">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="31">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="32">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="33">
                   <c:v>2024</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="34">
                   <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
@@ -908,206 +974,249 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'host country'!$X$27:$X$52</c:f>
+              <c:f>'host country (india)'!$X$18:$X$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
+                  <c:v>63.128319537359097</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>62.898333636700102</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>62.6630638065269</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>62.371240378322298</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>61.974428476754099</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>61.513380855523799</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>61.158625445787699</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>60.647957461240999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>59.878026680172397</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>59.607310099103998</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="10">
                   <c:v>58.890809220715099</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>58.2078564520654</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="12">
                   <c:v>57.164650542938602</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="13">
                   <c:v>55.999457323776298</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="14">
                   <c:v>55.020453312310899</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="15">
                   <c:v>54.273017899929599</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="16">
                   <c:v>53.368868437721702</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="17">
                   <c:v>52.879188395900101</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="18">
                   <c:v>51.944426618063801</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
                   <c:v>51.056070239904997</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="20">
                   <c:v>49.075305915587599</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="21">
                   <c:v>47.088154462332199</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="22">
                   <c:v>46.241883981632697</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="23">
                   <c:v>45.254711115223699</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="24">
                   <c:v>44.2796936892031</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="25">
                   <c:v>43.204850592630699</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="26">
                   <c:v>42.267106468212397</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="27">
                   <c:v>41.294998924914097</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="28">
                   <c:v>40.651814999322703</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="29">
                   <c:v>44.6754951957099</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="30">
                   <c:v>44.079186886638198</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="31">
                   <c:v>42.8609991503088</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="32">
                   <c:v>43.513581124579296</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="33">
                   <c:v>42.3547738876441</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="34">
                   <c:v>41.625128087757297</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
-            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
-              <c14:invertSolidFillFmt>
-                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                  <a:ln cmpd="sng">
-                    <a:noFill/>
-                  </a:ln>
-                </c14:spPr>
-              </c14:invertSolidFillFmt>
-            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2E45-4A14-86C0-1236895516D0}"/>
+              <c16:uniqueId val="{00000001-684E-4008-ABA6-554C62C9154A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="2"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>Employment in industry</c:v>
+            <c:v>Employment in Industry</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="E97132"/>
+              <a:schemeClr val="accent3"/>
             </a:solidFill>
-            <a:ln cmpd="sng">
+            <a:ln>
               <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="1"/>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'host country'!$B$27:$B$52</c:f>
+              <c:f>'host country (india)'!$B$18:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="10">
                   <c:v>2001</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>2002</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="12">
                   <c:v>2003</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="13">
                   <c:v>2004</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="14">
                   <c:v>2005</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="15">
                   <c:v>2006</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="16">
                   <c:v>2007</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="17">
                   <c:v>2008</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="18">
                   <c:v>2009</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="20">
                   <c:v>2011</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="21">
                   <c:v>2012</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="22">
                   <c:v>2013</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="23">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="24">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="25">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="26">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="27">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="28">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="29">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="30">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="31">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="32">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="33">
                   <c:v>2024</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="34">
                   <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
@@ -1115,206 +1224,249 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'host country'!$Y$27:$Y$52</c:f>
+              <c:f>'host country (india)'!$Y$18:$Y$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
+                  <c:v>14.584937300157501</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.6628055390629</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.7602607112643</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.851350268644399</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.000483006233299</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.2712590554772</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15.4726082964194</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15.7949095027609</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16.309428466052999</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>16.341359744203</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="10">
                   <c:v>16.7528345033409</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>17.056726884100499</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="12">
                   <c:v>17.6938066486046</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="13">
                   <c:v>18.418479484316101</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="14">
                   <c:v>19.0012317655898</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="15">
                   <c:v>19.5238914291204</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="16">
                   <c:v>20.3219145451672</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="17">
                   <c:v>20.751447752882001</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="18">
                   <c:v>21.5635579497653</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
                   <c:v>22.377888837294201</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="20">
                   <c:v>23.547382125569602</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="21">
                   <c:v>24.692037963598398</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="22">
                   <c:v>24.754673840533499</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="23">
                   <c:v>24.896015202228199</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="24">
                   <c:v>24.9480704919335</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="25">
                   <c:v>25.189478375845301</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="26">
                   <c:v>25.265722733605099</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="27">
                   <c:v>25.3658737784355</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="28">
                   <c:v>25.251113046720999</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="29">
                   <c:v>23.703647531851601</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="30">
                   <c:v>24.4704786231875</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="31">
                   <c:v>26.1203341573875</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="32">
                   <c:v>25.029211598620101</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="33">
                   <c:v>25.370925971161199</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="34">
                   <c:v>25.817307380638098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
-            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
-              <c14:invertSolidFillFmt>
-                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                  <a:ln cmpd="sng">
-                    <a:noFill/>
-                  </a:ln>
-                </c14:spPr>
-              </c14:invertSolidFillFmt>
-            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2E45-4A14-86C0-1236895516D0}"/>
+              <c16:uniqueId val="{00000002-684E-4008-ABA6-554C62C9154A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
+          <c:idx val="3"/>
           <c:order val="2"/>
           <c:tx>
-            <c:v>Employment in services</c:v>
+            <c:v>Employment in Services</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="196B24"/>
+              <a:schemeClr val="accent4"/>
             </a:solidFill>
-            <a:ln cmpd="sng">
+            <a:ln>
               <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="1"/>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'host country'!$B$27:$B$52</c:f>
+              <c:f>'host country (india)'!$B$18:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="10">
                   <c:v>2001</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>2002</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="12">
                   <c:v>2003</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="13">
                   <c:v>2004</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="14">
                   <c:v>2005</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="15">
                   <c:v>2006</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="16">
                   <c:v>2007</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="17">
                   <c:v>2008</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="18">
                   <c:v>2009</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="20">
                   <c:v>2011</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="21">
                   <c:v>2012</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="22">
                   <c:v>2013</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="23">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="24">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="25">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="26">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="27">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="28">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="29">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="30">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="31">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="32">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="33">
                   <c:v>2024</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="34">
                   <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
@@ -1322,106 +1474,121 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'host country'!$Z$27:$Z$52</c:f>
+              <c:f>'host country (india)'!$Z$18:$Z$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
+                  <c:v>22.286736307130901</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.4388544747388</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.576675808073102</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.777409353033299</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.025088517012598</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23.215360088998899</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23.368766257792899</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>23.557133035998099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>23.8125410413714</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>24.051330156692899</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="10">
                   <c:v>24.356356017475999</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>24.735416917017901</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="12">
                   <c:v>25.1415353719471</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="13">
                   <c:v>25.582063191907601</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="14">
                   <c:v>25.978314922099301</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="15">
                   <c:v>26.203090670950001</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="16">
                   <c:v>26.309209260168</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="17">
                   <c:v>26.369363851217901</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="18">
                   <c:v>26.4920231164018</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
                   <c:v>26.5660351341417</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="20">
                   <c:v>27.3773195279181</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="21">
                   <c:v>28.219815079124601</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="22">
                   <c:v>29.003443966457802</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="23">
                   <c:v>29.849273682548102</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="24">
                   <c:v>30.7722358188634</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="25">
                   <c:v>31.605663371419499</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="26">
                   <c:v>32.467165141529698</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="27">
                   <c:v>33.339127296650503</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="28">
                   <c:v>34.097073966908198</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="29">
                   <c:v>31.620857272438499</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="30">
                   <c:v>31.450327114961201</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="31">
                   <c:v>31.0186666923037</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="32">
                   <c:v>31.457207276800599</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="33">
                   <c:v>32.274309744917801</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="34">
                   <c:v>32.557562503110901</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
-            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
-              <c14:invertSolidFillFmt>
-                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                  <a:ln cmpd="sng">
-                    <a:noFill/>
-                  </a:ln>
-                </c14:spPr>
-              </c14:invertSolidFillFmt>
-            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-2E45-4A14-86C0-1236895516D0}"/>
+              <c16:uniqueId val="{00000003-684E-4008-ABA6-554C62C9154A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1435,11 +1602,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="2145031078"/>
-        <c:axId val="2040484350"/>
+        <c:axId val="10727631"/>
+        <c:axId val="2004889552"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2145031078"/>
+        <c:axId val="10727631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1448,72 +1615,104 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr sz="1000" b="0" i="0">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>Years</a:t>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Years (1991 - 2025)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="0.42066167390990589"/>
-              <c:y val="0.91513706620005852"/>
-            </c:manualLayout>
-          </c:layout>
           <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln>
-            <a:noFill/>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr sz="900" b="0" i="0">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2040484350"/>
+        <c:crossAx val="2004889552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2040484350"/>
+        <c:axId val="2004889552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1521,93 +1720,151 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr sz="1000" b="0" i="0">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>Employment Share(%)</a:t>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Employment Rate (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
           <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
+          <a:noFill/>
           <a:ln>
             <a:noFill/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr sz="900" b="0" i="0">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2145031078"/>
+        <c:crossAx val="10727631"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.81881751623152366"/>
-          <c:y val="0.34868088508803946"/>
-          <c:w val="0.16770728601716547"/>
-          <c:h val="0.22351149814882412"/>
+          <c:x val="0.13543135579464469"/>
+          <c:y val="0.90990052438871338"/>
+          <c:w val="0.7322489181267744"/>
+          <c:h val="5.6835442347253372E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
       <c:txPr>
-        <a:bodyPr/>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr sz="900" b="0" i="0">
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -1615,9 +1872,38 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1630,22 +1916,82 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Labour Productivity vs Manufacturing Growth (1991–2025)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
+          <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.4978664476756358E-2"/>
-          <c:y val="0.17171296296296296"/>
-          <c:w val="0.62278432603899969"/>
-          <c:h val="0.77736111111111106"/>
+          <c:x val="0.12896570855472334"/>
+          <c:y val="0.12972139753022677"/>
+          <c:w val="0.80409690658586375"/>
+          <c:h val="0.53936340949184636"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -1655,224 +2001,351 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Relationship between Manufacturing Growth and Labour productivity Growth</c:v>
+            <c:v>Labour Productivity vs Manufacturing Growth (1991–2025)</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln>
+            <a:ln w="19050" cap="rnd">
               <a:noFill/>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="7"/>
+            <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:ln cmpd="sng">
+              <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:schemeClr val="accent1"/>
                 </a:solidFill>
               </a:ln>
+              <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:trendlineType val="linear"/>
             <c:dispRSqr val="0"/>
             <c:dispEq val="0"/>
           </c:trendline>
           <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:trendlineType val="linear"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="0"/>
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-2.7729963987059701E-2"/>
-                  <c:y val="-4.3864003754497574E-2"/>
+                  <c:x val="1.4472553159754578E-2"/>
+                  <c:y val="4.9462088836724163E-2"/>
                 </c:manualLayout>
               </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200"/>
+                      <a:t>R² = 0.0015</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
               <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
             </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'host country'!$V$27:$V$52</c:f>
+              <c:f>'host country (india)'!$P$18:$P$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
-                  <c:v>7.2990978490111296</c:v>
+                  <c:v>1611.573240168538</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.2703251937848563</c:v>
+                  <c:v>1657.3327659305828</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.8667636076502419</c:v>
+                  <c:v>1692.8605842862344</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.3366103225509107</c:v>
+                  <c:v>1759.4330903999862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.3832533106597253</c:v>
+                  <c:v>1835.5247698138769</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.3490886911469175</c:v>
+                  <c:v>1913.4823383058394</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>17.787792317977249</c:v>
+                  <c:v>1931.3103062842606</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.98058873129321</c:v>
+                  <c:v>1989.0978607477293</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.6636154823950164</c:v>
+                  <c:v>2099.3346239843527</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.967629778823465</c:v>
+                  <c:v>2114.8403223013479</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.6951064643586449</c:v>
+                  <c:v>2168.9526353599404</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.1250562390001875</c:v>
+                  <c:v>2205.4297562025085</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.4530833068635332</c:v>
+                  <c:v>2328.9661937178694</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.9658474395659624</c:v>
+                  <c:v>2461.408525459628</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.8956697662977433</c:v>
+                  <c:v>2602.5098648732155</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>13.059393581395867</c:v>
+                  <c:v>2795.2731771491076</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.9268214208403975</c:v>
+                  <c:v>2992.6115343011502</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.5270636029121931</c:v>
+                  <c:v>3071.7999046753007</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.4115568850371574</c:v>
+                  <c:v>3296.3262308370158</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2.9749629420838488</c:v>
+                  <c:v>3556.2879334468016</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.0736109935103286</c:v>
+                  <c:v>3707.4594469246931</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.9552196717495889</c:v>
+                  <c:v>3876.6949238326238</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-1.744196563454409</c:v>
+                  <c:v>4054.4988321475198</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>12.707025648704672</c:v>
+                  <c:v>4281.3219187260511</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>9.2890336559855626</c:v>
+                  <c:v>4548.8229238013009</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>11.531872924542057</c:v>
+                  <c:v>4845.6041437431477</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5095.261672542686</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5347.1993215903403</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5413.2614821636535</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5163.9483242133047</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5394.2750920018307</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>5521.0953208257888</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5676.2654131508198</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5889.3415316188593</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6244.3754923770211</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'host country'!$Q$27:$Q$52</c:f>
+              <c:f>'host country (india)'!$V$18:$V$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
-                  <c:v>0.7386006089665903</c:v>
+                  <c:v>-2.3984638002645369</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5586949751226875</c:v>
+                  <c:v>3.0901834659496927</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.681785035223442</c:v>
+                  <c:v>8.5913410736169169</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.6014677941080917</c:v>
+                  <c:v>10.821183243712213</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.6867434185609076</c:v>
+                  <c:v>15.461462926030748</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.7325445148215985</c:v>
+                  <c:v>9.5012767788913948</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.4068235005626901</c:v>
+                  <c:v>5.1186909042598927E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.0597163370382496</c:v>
+                  <c:v>3.1318435932712987</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.6461292909720258</c:v>
+                  <c:v>5.3937745157569168</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.3092757708594265</c:v>
+                  <c:v>7.2990978490111296</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.8864069999459847</c:v>
+                  <c:v>2.2703251937848563</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.2508232265483157</c:v>
+                  <c:v>6.8667636076502419</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.5647290100046689</c:v>
+                  <c:v>6.3366103225509107</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.5864818307423985</c:v>
+                  <c:v>7.3832533106597253</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.5943557013775758</c:v>
+                  <c:v>9.3490886911469175</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>6.2480936998740626</c:v>
+                  <c:v>17.787792317977249</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6.52435201179114</c:v>
+                  <c:v>6.98058873129321</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.1522477155280262</c:v>
+                  <c:v>4.6636154823950164</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.9445478022315248</c:v>
+                  <c:v>10.967629778823465</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.235453488830601</c:v>
+                  <c:v>7.6951064643586449</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-4.6055997622102636</c:v>
+                  <c:v>3.1250562390001875</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.4602841339163337</c:v>
+                  <c:v>5.4530833068635332</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.3510152274583986</c:v>
+                  <c:v>4.9658474395659624</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.8104947172298198</c:v>
+                  <c:v>7.8956697662977433</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3.7538082340967045</c:v>
+                  <c:v>13.059393581395867</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.0284152116505147</c:v>
+                  <c:v>7.9268214208403975</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.5270636029121931</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5.4115568850371574</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-2.9749629420838488</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.0736109935103286</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>9.9552196717495889</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-1.744196563454409</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.707025648704672</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>9.2890336559855626</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>11.531872924542057</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-40BC-4711-B2E6-B0870AF9A6D2}"/>
+              <c16:uniqueId val="{00000000-73E9-42DF-B61B-D8CBE8C61487}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1884,11 +2357,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1084621397"/>
-        <c:axId val="730893513"/>
+        <c:axId val="24011695"/>
+        <c:axId val="2005012432"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1084621397"/>
+        <c:axId val="24011695"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1896,71 +2369,125 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr sz="1000" b="0" i="0">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>Manufacturing value added Growth(% annual)</a:t>
+                  <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>Labour Productivity (constant 2015 US$ per employed person)</a:t>
                 </a:r>
+                <a:endParaRPr lang="en-US" sz="1200"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.25994679792528702"/>
+              <c:y val="0.70196988534327931"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln>
-            <a:noFill/>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr sz="900" b="0" i="0">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="730893513"/>
+        <c:crossAx val="2005012432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="730893513"/>
+        <c:axId val="2005012432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1968,87 +2495,208 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr sz="1000" b="0" i="0">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>Labour Productivity Growth(%)</a:t>
+                  <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>Manufacturing Growth (%)</a:t>
                 </a:r>
+                <a:endParaRPr lang="en-US" sz="1200"/>
               </a:p>
             </c:rich>
           </c:tx>
           <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln>
-            <a:noFill/>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr sz="900" b="0" i="0">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1084621397"/>
+        <c:crossAx val="24011695"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
       <c:legendEntry>
+        <c:idx val="0"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="1"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
         <c:idx val="2"/>
         <c:delete val="1"/>
       </c:legendEntry>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.26670977103471821"/>
+          <c:y val="0.76637666193365173"/>
+          <c:w val="0.53759274274329638"/>
+          <c:h val="0.19853573946874584"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
       <c:txPr>
-        <a:bodyPr/>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr sz="900" b="0" i="0">
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -2056,9 +2704,38 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -2071,15 +2748,84 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Relationship Between Capital per Worker Growth and Manufacturing Growth in India (1992–2025)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.1831750339213029E-2"/>
+          <c:y val="0.17925553642809208"/>
+          <c:w val="0.60107032243657588"/>
+          <c:h val="0.68345289665644049"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -2087,234 +2833,359 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Relationship between Manufacturing Growth and Capital per Worker Growth</c:v>
+            <c:v>Relationship Between Capital per Worker Growth and Manufacturing Growth in India (1992–2025)</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln>
+            <a:ln w="19050" cap="rnd">
               <a:noFill/>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="7"/>
+            <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:ln cmpd="sng">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
               </a:ln>
+              <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:trendline>
-            <c:name>Linear (Relationship between Manufacturing Growth and Capital per Worker Growth)</c:name>
             <c:spPr>
-              <a:ln w="19050">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
-                  <a:srgbClr val="000000">
-                    <a:alpha val="0"/>
-                  </a:srgbClr>
+                  <a:schemeClr val="accent1"/>
                 </a:solidFill>
+                <a:prstDash val="sysDot"/>
               </a:ln>
+              <a:effectLst/>
             </c:spPr>
             <c:trendlineType val="linear"/>
             <c:dispRSqr val="0"/>
             <c:dispEq val="0"/>
           </c:trendline>
           <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:trendlineType val="linear"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="0"/>
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-7.4757938494682385E-3"/>
-                  <c:y val="-7.7695719069599059E-2"/>
+                  <c:x val="3.3843096614280067E-2"/>
+                  <c:y val="-5.8374673086565063E-2"/>
                 </c:manualLayout>
               </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200"/>
+                      <a:t>R² = 0.0211</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
               <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
             </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'host country'!$V$27:$V$52</c:f>
+              <c:f>'host country (india)'!$S$19:$S$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
-                  <c:v>7.2990978490111296</c:v>
+                  <c:v>7.8288140428024038</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.2703251937848563</c:v>
+                  <c:v>-3.2944607678232347</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.8667636076502419</c:v>
+                  <c:v>3.0556214388439291</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.3366103225509107</c:v>
+                  <c:v>8.7330960177334376</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.3832533106597253</c:v>
+                  <c:v>1.4880896446096055</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.3490886911469175</c:v>
+                  <c:v>5.8290116577961193</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>17.787792317977249</c:v>
+                  <c:v>7.2933075503791969</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.98058873129321</c:v>
+                  <c:v>13.19784429189694</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.6636154823950164</c:v>
+                  <c:v>-4.7280199267805703</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.967629778823465</c:v>
+                  <c:v>19.549665187247779</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.6951064643586449</c:v>
+                  <c:v>-2.7471096052982684</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.1250562390001875</c:v>
+                  <c:v>2.9145658178641169</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.4530833068635332</c:v>
+                  <c:v>9.1446146081960737</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.9658474395659624</c:v>
+                  <c:v>14.077431231950326</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.8956697662977433</c:v>
+                  <c:v>13.185023602367703</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>13.059393581395867</c:v>
+                  <c:v>15.679403700932792</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.9268214208403975</c:v>
+                  <c:v>2.7582898970766538</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.5270636029121931</c:v>
+                  <c:v>7.1252145490358645</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.4115568850371574</c:v>
+                  <c:v>10.420611879508833</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2.9749629420838488</c:v>
+                  <c:v>11.037972119489178</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.0736109935103286</c:v>
+                  <c:v>4.0517921524330918</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.9552196717495889</c:v>
+                  <c:v>-0.1562130706715556</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-1.744196563454409</c:v>
+                  <c:v>0.86864210182348323</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>12.707025648704672</c:v>
+                  <c:v>4.8063934370451555</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>9.2890336559855626</c:v>
+                  <c:v>6.7232625939447423</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>11.531872924542057</c:v>
+                  <c:v>6.1435182238880373</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9.6264305974305344</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-1.4200572980792965</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-5.9403908886824563</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>11.918631678332252</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.1459520795846401</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.851449512093295</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.0859293700615971</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5.5514673997552739</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'host country'!$S$27:$S$52</c:f>
+              <c:f>'host country (india)'!$V$19:$V$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
-                  <c:v>-4.7280199267805889</c:v>
+                  <c:v>3.0901834659496927</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19.549665187247818</c:v>
+                  <c:v>8.5913410736169169</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.7471096052982817</c:v>
+                  <c:v>10.821183243712213</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.9145658178641063</c:v>
+                  <c:v>15.461462926030748</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.1446146081961022</c:v>
+                  <c:v>9.5012767788913948</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.07743123195031</c:v>
+                  <c:v>5.1186909042598927E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>13.185023602367671</c:v>
+                  <c:v>3.1318435932712987</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15.679403700932818</c:v>
+                  <c:v>5.3937745157569168</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.7582898970766689</c:v>
+                  <c:v>7.2990978490111296</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.1252145490358325</c:v>
+                  <c:v>2.2703251937848563</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>10.420611879508842</c:v>
+                  <c:v>6.8667636076502419</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>11.037972119489185</c:v>
+                  <c:v>6.3366103225509107</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.0517921524330944</c:v>
+                  <c:v>7.3832533106597253</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.15621307067155962</c:v>
+                  <c:v>9.3490886911469175</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.86864210182349533</c:v>
+                  <c:v>17.787792317977249</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.8063934370451635</c:v>
+                  <c:v>6.98058873129321</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6.7232625939447326</c:v>
+                  <c:v>4.6636154823950164</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>6.1435182238880301</c:v>
+                  <c:v>10.967629778823465</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9.6264305974305344</c:v>
+                  <c:v>7.6951064643586449</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1.4200572980792956</c:v>
+                  <c:v>3.1250562390001875</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-5.9403908886824439</c:v>
+                  <c:v>5.4530833068635332</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>11.918631678332222</c:v>
+                  <c:v>4.9658474395659624</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>3.1459520795846361</c:v>
+                  <c:v>7.8956697662977433</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.851449512093327</c:v>
+                  <c:v>13.059393581395867</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3.0859293700615886</c:v>
+                  <c:v>7.9268214208403975</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>5.5514673997552819</c:v>
+                  <c:v>7.5270636029121931</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.4115568850371574</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-2.9749629420838488</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.0736109935103286</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.9552196717495889</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-1.744196563454409</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>12.707025648704672</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9.2890336559855626</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>11.531872924542057</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DC78-408D-A184-BD3453F808C3}"/>
+              <c16:uniqueId val="{00000000-5608-43BB-8A24-763FC58BD740}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2326,66 +3197,137 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="322908314"/>
-        <c:axId val="2024158"/>
+        <c:axId val="36265535"/>
+        <c:axId val="2005001872"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="322908314"/>
+        <c:axId val="36265535"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>Capital per Worker Growth (%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.23687162409261112"/>
+              <c:y val="0.88429936817830623"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln>
-            <a:noFill/>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr sz="900" b="0" i="0">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2024158"/>
+        <c:crossAx val="2005001872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2024158"/>
+        <c:axId val="2005001872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2393,79 +3335,164 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>Manufacturing Growth (%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.0243277848911651E-2"/>
+              <c:y val="0.28826352479895789"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln>
-            <a:noFill/>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr sz="900" b="0" i="0">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="322908314"/>
+        <c:crossAx val="36265535"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
       <c:legendEntry>
-        <c:idx val="1"/>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
       <c:txPr>
-        <a:bodyPr/>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr sz="900" b="0" i="0">
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -2473,9 +3500,38 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -2484,26 +3540,1690 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="8324850" cy="2876550"/>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>666751</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1474154703" name="Chart 1">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000CFD0DD57}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93745773-A007-44FB-A7AD-286FEC4DF003}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2515,26 +5235,33 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>209551</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="8191500" cy="2876550"/>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>533401</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="873057100" name="Chart 2">
+        <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00004CCB0934}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0236A5F5-CB3F-4AF2-B857-5B9CF355BE44}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2546,26 +5273,33 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>838199</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="8239125" cy="2762250"/>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>180974</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1477870060" name="Chart 3">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000EC811658}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FDA7EFF-DA38-48BF-924B-342AFF814CEA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2577,8 +5311,8 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8018,7 +10752,6 @@
         <v>84</v>
       </c>
       <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
       <c r="P4" s="29"/>
       <c r="Q4" s="29"/>
       <c r="R4" s="29"/>
@@ -9296,17 +12029,17 @@
         <v>92.358999999999995</v>
       </c>
       <c r="O18" s="36">
-        <f>N18*L18</f>
-        <v>29173956387.579998</v>
+        <f>N18*(L18/100)</f>
+        <v>291739563.87580001</v>
       </c>
       <c r="P18" s="34">
         <f>D18/O18</f>
-        <v>16.115732401685381</v>
+        <v>1611.573240168538</v>
       </c>
       <c r="Q18" s="29"/>
       <c r="R18" s="35">
         <f>I18/O18</f>
-        <v>3.1127710497812884</v>
+        <v>311.27710497812882</v>
       </c>
       <c r="S18" s="29"/>
       <c r="T18" s="32"/>
@@ -9399,24 +12132,24 @@
         <v>92.350999999999999</v>
       </c>
       <c r="O19" s="36">
-        <f t="shared" ref="O19:O26" si="4">N19*L19</f>
-        <v>29923724415.011002</v>
+        <f t="shared" ref="O19:O52" si="4">N19*(L19/100)</f>
+        <v>299237244.15011001</v>
       </c>
       <c r="P19" s="34">
         <f t="shared" ref="P19:P26" si="5">D19/O19</f>
-        <v>16.573327659305829</v>
+        <v>1657.3327659305828</v>
       </c>
       <c r="Q19" s="34">
         <f t="shared" ref="Q19:Q27" si="6">((P19-P18)/P18)*100</f>
-        <v>2.8394319675635216</v>
+        <v>2.8394319675635304</v>
       </c>
       <c r="R19" s="35">
         <f>I19/O19</f>
-        <v>3.3564641068468535</v>
+        <v>335.64641068468535</v>
       </c>
       <c r="S19" s="34">
         <f>((R19-R18)/R18)*100</f>
-        <v>7.8288140428023967</v>
+        <v>7.8288140428024038</v>
       </c>
       <c r="T19" s="32"/>
       <c r="U19">
@@ -9509,23 +12242,23 @@
       </c>
       <c r="O20" s="36">
         <f t="shared" si="4"/>
-        <v>30687493650.739998</v>
+        <v>306874936.50739998</v>
       </c>
       <c r="P20" s="34">
         <f t="shared" si="5"/>
-        <v>16.928605842862343</v>
+        <v>1692.8605842862344</v>
       </c>
       <c r="Q20" s="34">
         <f t="shared" si="6"/>
-        <v>2.1436744078189243</v>
+        <v>2.1436744078189327</v>
       </c>
       <c r="R20" s="35">
         <f t="shared" ref="R20:R26" si="7">I20/O20</f>
-        <v>3.245886713660715</v>
+        <v>324.58867136607154</v>
       </c>
       <c r="S20" s="34">
         <f>((R20-R19)/R19)*100</f>
-        <v>-3.2944607678232449</v>
+        <v>-3.2944607678232347</v>
       </c>
       <c r="T20" s="32"/>
       <c r="U20">
@@ -9616,23 +12349,23 @@
       </c>
       <c r="O21" s="36">
         <f t="shared" si="4"/>
-        <v>31492494017.872997</v>
+        <v>314924940.17873001</v>
       </c>
       <c r="P21" s="34">
         <f t="shared" si="5"/>
-        <v>17.594330903999865</v>
+        <v>1759.4330903999862</v>
       </c>
       <c r="Q21" s="34">
         <f t="shared" si="6"/>
-        <v>3.93254510924899</v>
+        <v>3.9325451092489692</v>
       </c>
       <c r="R21" s="35">
         <f t="shared" si="7"/>
-        <v>3.345068723963919</v>
+        <v>334.50687239639188</v>
       </c>
       <c r="S21" s="34">
         <f t="shared" ref="S21:S27" si="8">((R21-R20)/R20)*100</f>
-        <v>3.0556214388439438</v>
+        <v>3.0556214388439291</v>
       </c>
       <c r="T21" s="32"/>
       <c r="U21">
@@ -9723,19 +12456,19 @@
       </c>
       <c r="O22" s="36">
         <f t="shared" si="4"/>
-        <v>32473482459.210003</v>
+        <v>324734824.59210002</v>
       </c>
       <c r="P22" s="34">
         <f t="shared" si="5"/>
-        <v>18.355247698138768</v>
+        <v>1835.5247698138769</v>
       </c>
       <c r="Q22" s="34">
         <f t="shared" si="6"/>
-        <v>4.324783922109356</v>
+        <v>4.3247839221093738</v>
       </c>
       <c r="R22" s="35">
         <f t="shared" si="7"/>
-        <v>3.6371967874868587</v>
+        <v>363.71967874868585</v>
       </c>
       <c r="S22" s="34">
         <f t="shared" si="8"/>
@@ -9830,23 +12563,23 @@
       </c>
       <c r="O23" s="36">
         <f t="shared" si="4"/>
-        <v>33502185733.211998</v>
+        <v>335021857.33212</v>
       </c>
       <c r="P23" s="34">
         <f t="shared" si="5"/>
-        <v>19.134823383058396</v>
+        <v>1913.4823383058394</v>
       </c>
       <c r="Q23" s="34">
         <f t="shared" si="6"/>
-        <v>4.2471542620406995</v>
+        <v>4.2471542620406852</v>
       </c>
       <c r="R23" s="35">
         <f t="shared" si="7"/>
-        <v>3.6913215362355238</v>
+        <v>369.13215362355237</v>
       </c>
       <c r="S23" s="34">
         <f t="shared" si="8"/>
-        <v>1.4880896446096039</v>
+        <v>1.4880896446096055</v>
       </c>
       <c r="T23" s="32"/>
       <c r="U23">
@@ -9937,23 +12670,23 @@
       </c>
       <c r="O24" s="36">
         <f t="shared" si="4"/>
-        <v>34537180369.211998</v>
+        <v>345371803.69212002</v>
       </c>
       <c r="P24" s="34">
         <f t="shared" si="5"/>
-        <v>19.313103062842607</v>
+        <v>1931.3103062842606</v>
       </c>
       <c r="Q24" s="34">
         <f t="shared" si="6"/>
-        <v>0.93170277151372294</v>
+        <v>0.93170277151372605</v>
       </c>
       <c r="R24" s="35">
         <f t="shared" si="7"/>
-        <v>3.9064890989094314</v>
+        <v>390.64890989094312</v>
       </c>
       <c r="S24" s="34">
         <f t="shared" si="8"/>
-        <v>5.829011657796122</v>
+        <v>5.8290116577961193</v>
       </c>
       <c r="T24" s="32"/>
       <c r="U24">
@@ -10044,23 +12777,23 @@
       </c>
       <c r="O25" s="36">
         <f t="shared" si="4"/>
-        <v>35607670996.091995</v>
+        <v>356076709.96091998</v>
       </c>
       <c r="P25" s="34">
         <f t="shared" si="5"/>
-        <v>19.890978607477294</v>
+        <v>1989.0978607477293</v>
       </c>
       <c r="Q25" s="34">
         <f t="shared" si="6"/>
-        <v>2.9921423955246658</v>
+        <v>2.9921423955246702</v>
       </c>
       <c r="R25" s="35">
         <f t="shared" si="7"/>
-        <v>4.1914013633149327</v>
+        <v>419.1401363314933</v>
       </c>
       <c r="S25" s="34">
         <f t="shared" si="8"/>
-        <v>7.2933075503791844</v>
+        <v>7.2933075503791969</v>
       </c>
       <c r="T25" s="32"/>
       <c r="U25">
@@ -10151,23 +12884,23 @@
       </c>
       <c r="O26" s="36">
         <f t="shared" si="4"/>
-        <v>36722272473.445</v>
+        <v>367222724.73445004</v>
       </c>
       <c r="P26" s="34">
         <f t="shared" si="5"/>
-        <v>20.993346239843529</v>
+        <v>2099.3346239843527</v>
       </c>
       <c r="Q26" s="34">
         <f t="shared" si="6"/>
-        <v>5.5420482527281978</v>
+        <v>5.5420482527281907</v>
       </c>
       <c r="R26" s="35">
         <f t="shared" si="7"/>
-        <v>4.7445759888936836</v>
+        <v>474.45759888936834</v>
       </c>
       <c r="S26" s="34">
         <f t="shared" si="8"/>
-        <v>13.197844291896951</v>
+        <v>13.19784429189694</v>
       </c>
       <c r="T26" s="32"/>
       <c r="U26">
@@ -10256,25 +12989,25 @@
         <f t="shared" ref="N27:N52" si="9">100-M27</f>
         <v>92.411000000000001</v>
       </c>
-      <c r="O27" s="34">
-        <f>N27*L27</f>
-        <v>37853187835.881004</v>
+      <c r="O27" s="36">
+        <f t="shared" si="4"/>
+        <v>378531878.35881001</v>
       </c>
       <c r="P27" s="34">
         <f>D27/O27</f>
-        <v>21.148403223013478</v>
+        <v>2114.8403223013479</v>
       </c>
       <c r="Q27" s="34">
         <f t="shared" si="6"/>
-        <v>0.7386006089665903</v>
+        <v>0.73860060896660529</v>
       </c>
       <c r="R27" s="35">
         <f t="shared" ref="R27:R52" si="10">I27/O27</f>
-        <v>4.5202514906975431</v>
+        <v>452.02514906975438</v>
       </c>
       <c r="S27" s="34">
         <f t="shared" si="8"/>
-        <v>-4.7280199267805889</v>
+        <v>-4.7280199267805703</v>
       </c>
       <c r="T27" s="32"/>
       <c r="U27" s="11">
@@ -10363,25 +13096,25 @@
         <f>100-M28</f>
         <v>92.388999999999996</v>
       </c>
-      <c r="O28" s="34">
-        <f t="shared" ref="O28:O52" si="11">N28*L28</f>
-        <v>38689272378.657997</v>
+      <c r="O28" s="36">
+        <f t="shared" si="4"/>
+        <v>386892723.78658003</v>
       </c>
       <c r="P28" s="34">
-        <f t="shared" ref="P28:P52" si="12">D28/O28</f>
-        <v>21.689526353599408</v>
+        <f t="shared" ref="P28:P52" si="11">D28/O28</f>
+        <v>2168.9526353599404</v>
       </c>
       <c r="Q28" s="34">
-        <f t="shared" ref="Q28:Q52" si="13">((P28-P27)/P27)*100</f>
-        <v>2.5586949751226875</v>
+        <f t="shared" ref="Q28:Q52" si="12">((P28-P27)/P27)*100</f>
+        <v>2.5586949751226604</v>
       </c>
       <c r="R28" s="35">
         <f t="shared" si="10"/>
-        <v>5.4039455227504911</v>
+        <v>540.39455227504902</v>
       </c>
       <c r="S28" s="34">
         <f>((R28-R27)/R27)*100</f>
-        <v>19.549665187247818</v>
+        <v>19.549665187247779</v>
       </c>
       <c r="T28" s="32"/>
       <c r="U28" s="11">
@@ -10420,7 +13153,7 @@
         <v>5128093561.6268797</v>
       </c>
       <c r="AH28" s="34">
-        <f t="shared" ref="AH28:AH52" si="14">((AG28-AG27)/AG27)*100</f>
+        <f t="shared" ref="AH28:AH52" si="13">((AG28-AG27)/AG27)*100</f>
         <v>43.074292714990889</v>
       </c>
       <c r="AI28" s="29">
@@ -10449,7 +13182,7 @@
         <v>793.61591290100171</v>
       </c>
       <c r="G29" s="34">
-        <f t="shared" ref="G29:G52" si="15">((F29-F28)/F28)*100</f>
+        <f t="shared" ref="G29:G52" si="14">((F29-F28)/F28)*100</f>
         <v>1.9407054852304837</v>
       </c>
       <c r="H29" s="30"/>
@@ -10470,25 +13203,25 @@
         <f t="shared" si="9"/>
         <v>92.319000000000003</v>
       </c>
-      <c r="O29" s="34">
+      <c r="O29" s="36">
+        <f t="shared" si="4"/>
+        <v>394967522.82606006</v>
+      </c>
+      <c r="P29" s="34">
         <f t="shared" si="11"/>
-        <v>39496752282.606003</v>
-      </c>
-      <c r="P29" s="34">
+        <v>2205.4297562025085</v>
+      </c>
+      <c r="Q29" s="34">
         <f t="shared" si="12"/>
-        <v>22.054297562025088</v>
-      </c>
-      <c r="Q29" s="34">
-        <f t="shared" si="13"/>
-        <v>1.681785035223442</v>
+        <v>1.6817850352234529</v>
       </c>
       <c r="R29" s="35">
         <f t="shared" si="10"/>
-        <v>5.2554932162299259</v>
+        <v>525.54932162299258</v>
       </c>
       <c r="S29" s="34">
-        <f t="shared" ref="S29:S52" si="16">((R29-R28)/R28)*100</f>
-        <v>-2.7471096052982817</v>
+        <f t="shared" ref="S29:S52" si="15">((R29-R28)/R28)*100</f>
+        <v>-2.7471096052982684</v>
       </c>
       <c r="T29" s="32"/>
       <c r="U29" s="11">
@@ -10527,7 +13260,7 @@
         <v>5208967106.2789402</v>
       </c>
       <c r="AH29" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.5770684306002307</v>
       </c>
       <c r="AI29" s="29">
@@ -10556,7 +13289,7 @@
         <v>841.27889456240837</v>
       </c>
       <c r="G30" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.0057996426984825</v>
       </c>
       <c r="H30" s="30"/>
@@ -10577,25 +13310,25 @@
         <f t="shared" si="9"/>
         <v>92.367000000000004</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="36">
+        <f t="shared" si="4"/>
+        <v>403416245.74283999</v>
+      </c>
+      <c r="P30" s="34">
         <f t="shared" si="11"/>
-        <v>40341624574.284004</v>
-      </c>
-      <c r="P30" s="34">
+        <v>2328.9661937178694</v>
+      </c>
+      <c r="Q30" s="34">
         <f t="shared" si="12"/>
-        <v>23.289661937178689</v>
-      </c>
-      <c r="Q30" s="34">
-        <f t="shared" si="13"/>
-        <v>5.6014677941080917</v>
+        <v>5.6014677941081237</v>
       </c>
       <c r="R30" s="35">
         <f t="shared" si="10"/>
-        <v>5.4086680250703303</v>
+        <v>540.86680250703307</v>
       </c>
       <c r="S30" s="34">
-        <f t="shared" si="16"/>
-        <v>2.9145658178641063</v>
+        <f t="shared" si="15"/>
+        <v>2.9145658178641169</v>
       </c>
       <c r="T30" s="32"/>
       <c r="U30" s="11">
@@ -10634,7 +13367,7 @@
         <v>3681984671.4342799</v>
       </c>
       <c r="AH30" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-29.314495632042302</v>
       </c>
       <c r="AI30" s="29">
@@ -10663,7 +13396,7 @@
         <v>892.5966145807181</v>
       </c>
       <c r="G31" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.0999652255632375</v>
       </c>
       <c r="H31" s="30"/>
@@ -10684,25 +13417,25 @@
         <f t="shared" si="9"/>
         <v>92.402000000000001</v>
       </c>
-      <c r="O31" s="34">
+      <c r="O31" s="36">
+        <f t="shared" si="4"/>
+        <v>411952005.61308002</v>
+      </c>
+      <c r="P31" s="34">
         <f t="shared" si="11"/>
-        <v>41195200561.307999</v>
-      </c>
-      <c r="P31" s="34">
+        <v>2461.408525459628</v>
+      </c>
+      <c r="Q31" s="34">
         <f t="shared" si="12"/>
-        <v>24.614085254596283</v>
-      </c>
-      <c r="Q31" s="34">
-        <f t="shared" si="13"/>
-        <v>5.6867434185609076</v>
+        <v>5.686743418560873</v>
       </c>
       <c r="R31" s="35">
         <f t="shared" si="10"/>
-        <v>5.9032698713997434</v>
+        <v>590.32698713997422</v>
       </c>
       <c r="S31" s="34">
-        <f t="shared" si="16"/>
-        <v>9.1446146081961022</v>
+        <f t="shared" si="15"/>
+        <v>9.1446146081960737</v>
       </c>
       <c r="T31" s="32"/>
       <c r="U31" s="11">
@@ -10741,7 +13474,7 @@
         <v>5429250989.8571701</v>
       </c>
       <c r="AH31" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>47.454470193170586</v>
       </c>
       <c r="AI31" s="29">
@@ -10770,7 +13503,7 @@
         <v>947.73256564427152</v>
       </c>
       <c r="G32" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.1770289247010624</v>
       </c>
       <c r="H32" s="30"/>
@@ -10791,25 +13524,25 @@
         <f t="shared" si="9"/>
         <v>92.448999999999998</v>
       </c>
-      <c r="O32" s="34">
+      <c r="O32" s="36">
+        <f t="shared" si="4"/>
+        <v>420488071.11478996</v>
+      </c>
+      <c r="P32" s="34">
         <f t="shared" si="11"/>
-        <v>42048807111.478996</v>
-      </c>
-      <c r="P32" s="34">
+        <v>2602.5098648732155</v>
+      </c>
+      <c r="Q32" s="34">
         <f t="shared" si="12"/>
-        <v>26.025098648732154</v>
-      </c>
-      <c r="Q32" s="34">
-        <f t="shared" si="13"/>
-        <v>5.7325445148215985</v>
+        <v>5.7325445148216163</v>
       </c>
       <c r="R32" s="35">
         <f t="shared" si="10"/>
-        <v>6.7342986279824837</v>
+        <v>673.42986279824834</v>
       </c>
       <c r="S32" s="34">
-        <f t="shared" si="16"/>
-        <v>14.07743123195031</v>
+        <f t="shared" si="15"/>
+        <v>14.077431231950326</v>
       </c>
       <c r="T32" s="32"/>
       <c r="U32" s="11">
@@ -10848,7 +13581,7 @@
         <v>7269407225.6143799</v>
       </c>
       <c r="AH32" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>33.893372017520591</v>
       </c>
       <c r="AI32" s="29">
@@ -10877,7 +13610,7 @@
         <v>1008.2327534481848</v>
       </c>
       <c r="G33" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.383677209908373</v>
       </c>
       <c r="H33" s="30"/>
@@ -10898,25 +13631,25 @@
         <f t="shared" si="9"/>
         <v>92.447000000000003</v>
       </c>
-      <c r="O33" s="34">
+      <c r="O33" s="36">
+        <f t="shared" si="4"/>
+        <v>423048066.42619997</v>
+      </c>
+      <c r="P33" s="34">
         <f t="shared" si="11"/>
-        <v>42304806642.620003</v>
-      </c>
-      <c r="P33" s="34">
+        <v>2795.2731771491076</v>
+      </c>
+      <c r="Q33" s="34">
         <f t="shared" si="12"/>
-        <v>27.95273177149107</v>
-      </c>
-      <c r="Q33" s="34">
-        <f t="shared" si="13"/>
-        <v>7.4068235005626901</v>
+        <v>7.4068235005627061</v>
       </c>
       <c r="R33" s="35">
         <f t="shared" si="10"/>
-        <v>7.6222174915358964</v>
+        <v>762.22174915358983</v>
       </c>
       <c r="S33" s="34">
-        <f t="shared" si="16"/>
-        <v>13.185023602367671</v>
+        <f t="shared" si="15"/>
+        <v>13.185023602367703</v>
       </c>
       <c r="T33" s="32"/>
       <c r="U33" s="11">
@@ -10955,7 +13688,7 @@
         <v>20029119267.139599</v>
       </c>
       <c r="AH33" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>175.52616940436738</v>
       </c>
       <c r="AI33" s="29">
@@ -10984,7 +13717,7 @@
         <v>1069.246968122337</v>
       </c>
       <c r="G34" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.0516001355323787</v>
       </c>
       <c r="H34" s="30"/>
@@ -11005,25 +13738,25 @@
         <f t="shared" si="9"/>
         <v>92.438000000000002</v>
       </c>
-      <c r="O34" s="34">
+      <c r="O34" s="36">
+        <f t="shared" si="4"/>
+        <v>425423317.01850003</v>
+      </c>
+      <c r="P34" s="34">
         <f t="shared" si="11"/>
-        <v>42542331701.849998</v>
-      </c>
-      <c r="P34" s="34">
+        <v>2992.6115343011502</v>
+      </c>
+      <c r="Q34" s="34">
         <f t="shared" si="12"/>
-        <v>29.926115343011507</v>
-      </c>
-      <c r="Q34" s="34">
-        <f t="shared" si="13"/>
-        <v>7.0597163370382496</v>
+        <v>7.0597163370382106</v>
       </c>
       <c r="R34" s="35">
         <f t="shared" si="10"/>
-        <v>8.8173357429969244</v>
+        <v>881.73357429969246</v>
       </c>
       <c r="S34" s="34">
-        <f t="shared" si="16"/>
-        <v>15.679403700932818</v>
+        <f t="shared" si="15"/>
+        <v>15.679403700932792</v>
       </c>
       <c r="T34" s="32"/>
       <c r="U34" s="11">
@@ -11062,7 +13795,7 @@
         <v>25227740886.6819</v>
       </c>
       <c r="AH34" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>25.955318105630948</v>
       </c>
       <c r="AI34" s="29">
@@ -11091,7 +13824,7 @@
         <v>1086.506052510045</v>
       </c>
       <c r="G35" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.6141345173057708</v>
       </c>
       <c r="H35" s="30"/>
@@ -11112,25 +13845,25 @@
         <f t="shared" si="9"/>
         <v>92.370999999999995</v>
       </c>
-      <c r="O35" s="34">
+      <c r="O35" s="36">
+        <f t="shared" si="4"/>
+        <v>427249281.89586002</v>
+      </c>
+      <c r="P35" s="34">
         <f t="shared" si="11"/>
-        <v>42724928189.585999</v>
-      </c>
-      <c r="P35" s="34">
+        <v>3071.7999046753007</v>
+      </c>
+      <c r="Q35" s="34">
         <f t="shared" si="12"/>
-        <v>30.717999046753008</v>
-      </c>
-      <c r="Q35" s="34">
-        <f t="shared" si="13"/>
-        <v>2.6461292909720258</v>
+        <v>2.6461292909720395</v>
       </c>
       <c r="R35" s="35">
         <f t="shared" si="10"/>
-        <v>9.0605434239873386</v>
+        <v>906.05434239873375</v>
       </c>
       <c r="S35" s="34">
-        <f t="shared" si="16"/>
-        <v>2.7582898970766689</v>
+        <f t="shared" si="15"/>
+        <v>2.7582898970766538</v>
       </c>
       <c r="T35" s="32"/>
       <c r="U35" s="11">
@@ -11169,7 +13902,7 @@
         <v>43406277075.810799</v>
       </c>
       <c r="AH35" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>72.057725147817806</v>
       </c>
       <c r="AI35" s="29">
@@ -11198,7 +13931,7 @@
         <v>1155.1016327381701</v>
       </c>
       <c r="G36" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.3134098581094547</v>
       </c>
       <c r="H36" s="30"/>
@@ -11219,25 +13952,25 @@
         <f t="shared" si="9"/>
         <v>92.364000000000004</v>
       </c>
-      <c r="O36" s="34">
+      <c r="O36" s="36">
+        <f t="shared" si="4"/>
+        <v>429449497.41575998</v>
+      </c>
+      <c r="P36" s="34">
         <f t="shared" si="11"/>
-        <v>42944949741.576004</v>
-      </c>
-      <c r="P36" s="34">
+        <v>3296.3262308370158</v>
+      </c>
+      <c r="Q36" s="34">
         <f t="shared" si="12"/>
-        <v>32.963262308370155</v>
-      </c>
-      <c r="Q36" s="34">
-        <f t="shared" si="13"/>
-        <v>7.3092757708594265</v>
+        <v>7.3092757708594398</v>
       </c>
       <c r="R36" s="35">
         <f t="shared" si="10"/>
-        <v>9.7061265822549938</v>
+        <v>970.61265822549956</v>
       </c>
       <c r="S36" s="34">
-        <f t="shared" si="16"/>
-        <v>7.1252145490358325</v>
+        <f t="shared" si="15"/>
+        <v>7.1252145490358645</v>
       </c>
       <c r="T36" s="32"/>
       <c r="U36" s="11">
@@ -11276,7 +14009,7 @@
         <v>35581372929.664101</v>
       </c>
       <c r="AH36" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-18.027125736861031</v>
       </c>
       <c r="AI36" s="29">
@@ -11305,7 +14038,7 @@
         <v>1235.1593913293866</v>
       </c>
       <c r="G37" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.9307978036044728</v>
       </c>
       <c r="H37" s="30"/>
@@ -11326,25 +14059,25 @@
         <f t="shared" si="9"/>
         <v>92.369</v>
       </c>
-      <c r="O37" s="34">
+      <c r="O37" s="36">
+        <f t="shared" si="4"/>
+        <v>431882333.61940998</v>
+      </c>
+      <c r="P37" s="34">
         <f t="shared" si="11"/>
-        <v>43188233361.941002</v>
-      </c>
-      <c r="P37" s="34">
+        <v>3556.2879334468016</v>
+      </c>
+      <c r="Q37" s="34">
         <f t="shared" si="12"/>
-        <v>35.562879334468015</v>
-      </c>
-      <c r="Q37" s="34">
-        <f t="shared" si="13"/>
-        <v>7.8864069999459847</v>
+        <v>7.8864069999459758</v>
       </c>
       <c r="R37" s="35">
         <f t="shared" si="10"/>
-        <v>10.717564361925623</v>
+        <v>1071.7564361925624</v>
       </c>
       <c r="S37" s="34">
-        <f t="shared" si="16"/>
-        <v>10.420611879508842</v>
+        <f t="shared" si="15"/>
+        <v>10.420611879508833</v>
       </c>
       <c r="T37" s="32"/>
       <c r="U37" s="11">
@@ -11383,7 +14116,7 @@
         <v>27396885033.783798</v>
       </c>
       <c r="AH37" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-23.002170017607487</v>
       </c>
       <c r="AI37" s="29">
@@ -11412,7 +14145,7 @@
         <v>1281.610543549368</v>
       </c>
       <c r="G38" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>3.7607415323124087</v>
       </c>
       <c r="H38" s="30"/>
@@ -11433,25 +14166,25 @@
         <f t="shared" si="9"/>
         <v>92.391000000000005</v>
       </c>
-      <c r="O38" s="34">
+      <c r="O38" s="36">
+        <f t="shared" si="4"/>
+        <v>435985672.12239003</v>
+      </c>
+      <c r="P38" s="34">
         <f t="shared" si="11"/>
-        <v>43598567212.239006</v>
-      </c>
-      <c r="P38" s="34">
+        <v>3707.4594469246931</v>
+      </c>
+      <c r="Q38" s="34">
         <f t="shared" si="12"/>
-        <v>37.074594469246932</v>
-      </c>
-      <c r="Q38" s="34">
-        <f t="shared" si="13"/>
-        <v>4.2508232265483157</v>
+        <v>4.2508232265483086</v>
       </c>
       <c r="R38" s="35">
         <f t="shared" si="10"/>
-        <v>11.900566128083282</v>
+        <v>1190.0566128083283</v>
       </c>
       <c r="S38" s="34">
-        <f t="shared" si="16"/>
-        <v>11.037972119489185</v>
+        <f t="shared" si="15"/>
+        <v>11.037972119489178</v>
       </c>
       <c r="T38" s="32"/>
       <c r="U38" s="11">
@@ -11490,7 +14223,7 @@
         <v>36498654597.858902</v>
       </c>
       <c r="AH38" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>33.221913925073885</v>
       </c>
       <c r="AI38" s="29">
@@ -11519,7 +14252,7 @@
         <v>1333.0962655764886</v>
       </c>
       <c r="G39" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>4.0172673583453031</v>
       </c>
       <c r="H39" s="30"/>
@@ -11540,25 +14273,25 @@
         <f t="shared" si="9"/>
         <v>92.355000000000004</v>
       </c>
-      <c r="O39" s="34">
+      <c r="O39" s="36">
+        <f t="shared" si="4"/>
+        <v>439703468.2881</v>
+      </c>
+      <c r="P39" s="34">
         <f t="shared" si="11"/>
-        <v>43970346828.810005</v>
-      </c>
-      <c r="P39" s="34">
+        <v>3876.6949238326238</v>
+      </c>
+      <c r="Q39" s="34">
         <f t="shared" si="12"/>
-        <v>38.766949238326234</v>
-      </c>
-      <c r="Q39" s="34">
-        <f t="shared" si="13"/>
-        <v>4.5647290100046689</v>
+        <v>4.564729010004684</v>
       </c>
       <c r="R39" s="35">
         <f t="shared" si="10"/>
-        <v>12.382752332556072</v>
+        <v>1238.2752332556072</v>
       </c>
       <c r="S39" s="34">
-        <f t="shared" si="16"/>
-        <v>4.0517921524330944</v>
+        <f t="shared" si="15"/>
+        <v>4.0517921524330918</v>
       </c>
       <c r="T39" s="32"/>
       <c r="U39" s="11">
@@ -11597,7 +14330,7 @@
         <v>23995685014.2141</v>
       </c>
       <c r="AH39" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-34.255973874659631</v>
       </c>
       <c r="AI39" s="29">
@@ -11626,7 +14359,7 @@
         <v>1399.4537980280961</v>
       </c>
       <c r="G40" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>4.9776999729956986</v>
       </c>
       <c r="H40" s="30"/>
@@ -11647,25 +14380,25 @@
         <f t="shared" si="9"/>
         <v>92.322000000000003</v>
       </c>
-      <c r="O40" s="34">
+      <c r="O40" s="36">
+        <f t="shared" si="4"/>
+        <v>447269466.79259998</v>
+      </c>
+      <c r="P40" s="34">
         <f t="shared" si="11"/>
-        <v>44726946679.260002</v>
-      </c>
-      <c r="P40" s="34">
+        <v>4054.4988321475198</v>
+      </c>
+      <c r="Q40" s="34">
         <f t="shared" si="12"/>
-        <v>40.544988321475195</v>
-      </c>
-      <c r="Q40" s="34">
-        <f t="shared" si="13"/>
-        <v>4.5864818307423985</v>
+        <v>4.5864818307423958</v>
       </c>
       <c r="R40" s="35">
         <f t="shared" si="10"/>
-        <v>12.363408854903732</v>
+        <v>1236.3408854903732</v>
       </c>
       <c r="S40" s="34">
-        <f t="shared" si="16"/>
-        <v>-0.15621307067155962</v>
+        <f t="shared" si="15"/>
+        <v>-0.1562130706715556</v>
       </c>
       <c r="T40" s="32"/>
       <c r="U40" s="11">
@@ -11704,7 +14437,7 @@
         <v>28153031270.320202</v>
       </c>
       <c r="AH40" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>17.325391017774461</v>
       </c>
       <c r="AI40" s="29">
@@ -11733,7 +14466,7 @@
         <v>1484.3164068296119</v>
       </c>
       <c r="G41" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.0639807417073452</v>
       </c>
       <c r="H41" s="30"/>
@@ -11754,25 +14487,25 @@
         <f t="shared" si="9"/>
         <v>92.343999999999994</v>
       </c>
-      <c r="O41" s="34">
+      <c r="O41" s="36">
+        <f t="shared" si="4"/>
+        <v>454961014.81879997</v>
+      </c>
+      <c r="P41" s="34">
         <f t="shared" si="11"/>
-        <v>45496101481.879997</v>
-      </c>
-      <c r="P41" s="34">
+        <v>4281.3219187260511</v>
+      </c>
+      <c r="Q41" s="34">
         <f t="shared" si="12"/>
-        <v>42.813219187260515</v>
-      </c>
-      <c r="Q41" s="34">
-        <f t="shared" si="13"/>
-        <v>5.5943557013775758</v>
+        <v>5.594355701377558</v>
       </c>
       <c r="R41" s="35">
         <f t="shared" si="10"/>
-        <v>12.470802629437999</v>
+        <v>1247.0802629437999</v>
       </c>
       <c r="S41" s="34">
-        <f t="shared" si="16"/>
-        <v>0.86864210182349533</v>
+        <f t="shared" si="15"/>
+        <v>0.86864210182348323</v>
       </c>
       <c r="T41" s="32"/>
       <c r="U41" s="11">
@@ -11811,7 +14544,7 @@
         <v>34576643694.138199</v>
       </c>
       <c r="AH41" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>22.816770109547559</v>
       </c>
       <c r="AI41" s="29">
@@ -11840,7 +14573,7 @@
         <v>1583.9981590798479</v>
       </c>
       <c r="G42" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.7156673463677983</v>
       </c>
       <c r="H42" s="30"/>
@@ -11861,25 +14594,25 @@
         <f t="shared" si="9"/>
         <v>92.370999999999995</v>
       </c>
-      <c r="O42" s="34">
+      <c r="O42" s="36">
+        <f t="shared" si="4"/>
+        <v>462446746.17649001</v>
+      </c>
+      <c r="P42" s="34">
         <f t="shared" si="11"/>
-        <v>46244674617.648994</v>
-      </c>
-      <c r="P42" s="34">
+        <v>4548.8229238013009</v>
+      </c>
+      <c r="Q42" s="34">
         <f t="shared" si="12"/>
-        <v>45.488229238013012</v>
-      </c>
-      <c r="Q42" s="34">
-        <f t="shared" si="13"/>
-        <v>6.2480936998740626</v>
+        <v>6.2480936998740653</v>
       </c>
       <c r="R42" s="35">
         <f t="shared" si="10"/>
-        <v>13.070198468566163</v>
+        <v>1307.0198468566161</v>
       </c>
       <c r="S42" s="34">
-        <f t="shared" si="16"/>
-        <v>4.8063934370451635</v>
+        <f t="shared" si="15"/>
+        <v>4.8063934370451555</v>
       </c>
       <c r="T42" s="32"/>
       <c r="U42" s="11">
@@ -11918,7 +14651,7 @@
         <v>44009492129.531898</v>
       </c>
       <c r="AH42" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>27.28098342579403</v>
       </c>
       <c r="AI42" s="29">
@@ -11947,7 +14680,7 @@
         <v>1694.465349737867</v>
       </c>
       <c r="G43" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.973946909268502</v>
       </c>
       <c r="H43" s="30"/>
@@ -11968,25 +14701,25 @@
         <f t="shared" si="9"/>
         <v>92.388999999999996</v>
       </c>
-      <c r="O43" s="34">
+      <c r="O43" s="36">
+        <f t="shared" si="4"/>
+        <v>469965555.17031997</v>
+      </c>
+      <c r="P43" s="34">
         <f t="shared" si="11"/>
-        <v>46996555517.031998</v>
-      </c>
-      <c r="P43" s="34">
+        <v>4845.6041437431477</v>
+      </c>
+      <c r="Q43" s="34">
         <f t="shared" si="12"/>
-        <v>48.45604143743148</v>
-      </c>
-      <c r="Q43" s="34">
-        <f t="shared" si="13"/>
         <v>6.52435201179114</v>
       </c>
       <c r="R43" s="35">
         <f t="shared" si="10"/>
-        <v>13.948942233157609</v>
+        <v>1394.8942233157609</v>
       </c>
       <c r="S43" s="34">
-        <f t="shared" si="16"/>
-        <v>6.7232625939447326</v>
+        <f t="shared" si="15"/>
+        <v>6.7232625939447423</v>
       </c>
       <c r="T43" s="32"/>
       <c r="U43" s="11">
@@ -12025,7 +14758,7 @@
         <v>44458571545.797997</v>
       </c>
       <c r="AH43" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0204149026404012</v>
       </c>
       <c r="AI43" s="29">
@@ -12054,7 +14787,7 @@
         <v>1788.6977031848121</v>
       </c>
       <c r="G44" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>5.5611850346495917</v>
       </c>
       <c r="H44" s="30"/>
@@ -12075,25 +14808,25 @@
         <f t="shared" si="9"/>
         <v>92.373999999999995</v>
       </c>
-      <c r="O44" s="34">
+      <c r="O44" s="36">
+        <f t="shared" si="4"/>
+        <v>477309356.18161994</v>
+      </c>
+      <c r="P44" s="34">
         <f t="shared" si="11"/>
-        <v>47730935618.161995</v>
-      </c>
-      <c r="P44" s="34">
+        <v>5095.261672542686</v>
+      </c>
+      <c r="Q44" s="34">
         <f t="shared" si="12"/>
-        <v>50.952616725426857</v>
-      </c>
-      <c r="Q44" s="34">
-        <f t="shared" si="13"/>
-        <v>5.1522477155280262</v>
+        <v>5.1522477155280395</v>
       </c>
       <c r="R44" s="35">
         <f t="shared" si="10"/>
-        <v>14.805898041291261</v>
+        <v>1480.5898041291262</v>
       </c>
       <c r="S44" s="34">
-        <f t="shared" si="16"/>
-        <v>6.1435182238880301</v>
+        <f t="shared" si="15"/>
+        <v>6.1435182238880373</v>
       </c>
       <c r="T44" s="32"/>
       <c r="U44" s="11">
@@ -12132,7 +14865,7 @@
         <v>39966091358.738403</v>
       </c>
       <c r="AH44" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-10.104868489604453</v>
       </c>
       <c r="AI44" s="29">
@@ -12161,7 +14894,7 @@
         <v>1883.3577270505514</v>
       </c>
       <c r="G45" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>5.2921197191227565</v>
       </c>
       <c r="H45" s="30"/>
@@ -12182,24 +14915,24 @@
         <f t="shared" si="9"/>
         <v>92.347999999999999</v>
       </c>
-      <c r="O45" s="34">
+      <c r="O45" s="36">
+        <f t="shared" si="4"/>
+        <v>484173978.66412002</v>
+      </c>
+      <c r="P45" s="34">
         <f t="shared" si="11"/>
-        <v>48417397866.412003</v>
-      </c>
-      <c r="P45" s="34">
+        <v>5347.1993215903403</v>
+      </c>
+      <c r="Q45" s="34">
         <f t="shared" si="12"/>
-        <v>53.471993215903403</v>
-      </c>
-      <c r="Q45" s="34">
-        <f t="shared" si="13"/>
-        <v>4.9445478022315248</v>
+        <v>4.9445478022315186</v>
       </c>
       <c r="R45" s="35">
         <f t="shared" si="10"/>
-        <v>16.231177540562491</v>
+        <v>1623.1177540562492</v>
       </c>
       <c r="S45" s="34">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>9.6264305974305344</v>
       </c>
       <c r="T45" s="32"/>
@@ -12239,7 +14972,7 @@
         <v>42117450737.264397</v>
       </c>
       <c r="AH45" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>5.3829616692191458</v>
       </c>
       <c r="AI45" s="29">
@@ -12268,7 +15001,7 @@
         <v>1936.0306774106321</v>
       </c>
       <c r="G46" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2.7967575996605598</v>
       </c>
       <c r="H46" s="30"/>
@@ -12289,25 +15022,25 @@
         <f t="shared" si="9"/>
         <v>93.49</v>
       </c>
-      <c r="O46" s="34">
+      <c r="O46" s="36">
+        <f t="shared" si="4"/>
+        <v>496780971.09219998</v>
+      </c>
+      <c r="P46" s="34">
         <f t="shared" si="11"/>
-        <v>49678097109.219994</v>
-      </c>
-      <c r="P46" s="34">
+        <v>5413.2614821636535</v>
+      </c>
+      <c r="Q46" s="34">
         <f t="shared" si="12"/>
-        <v>54.132614821636544</v>
-      </c>
-      <c r="Q46" s="34">
-        <f t="shared" si="13"/>
-        <v>1.235453488830601</v>
+        <v>1.2354534888305828</v>
       </c>
       <c r="R46" s="35">
         <f t="shared" si="10"/>
-        <v>16.000685519333526</v>
+        <v>1600.0685519333526</v>
       </c>
       <c r="S46" s="34">
-        <f t="shared" si="16"/>
-        <v>-1.4200572980792956</v>
+        <f t="shared" si="15"/>
+        <v>-1.4200572980792965</v>
       </c>
       <c r="T46" s="32"/>
       <c r="U46" s="11">
@@ -12346,7 +15079,7 @@
         <v>50610647353.591103</v>
       </c>
       <c r="AH46" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>20.165504957336253</v>
       </c>
       <c r="AI46" s="29">
@@ -12375,7 +15108,7 @@
         <v>1806.5011058386517</v>
       </c>
       <c r="G47" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-6.6904710283424453</v>
       </c>
       <c r="H47" s="30"/>
@@ -12396,25 +15129,25 @@
         <f t="shared" si="9"/>
         <v>92.141000000000005</v>
       </c>
-      <c r="O47" s="34">
+      <c r="O47" s="36">
+        <f t="shared" si="4"/>
+        <v>490676950.65914005</v>
+      </c>
+      <c r="P47" s="34">
         <f t="shared" si="11"/>
-        <v>49067695065.914001</v>
-      </c>
-      <c r="P47" s="34">
+        <v>5163.9483242133047</v>
+      </c>
+      <c r="Q47" s="34">
         <f t="shared" si="12"/>
-        <v>51.639483242133053</v>
-      </c>
-      <c r="Q47" s="34">
-        <f t="shared" si="13"/>
-        <v>-4.6055997622102636</v>
+        <v>-4.6055997622102591</v>
       </c>
       <c r="R47" s="35">
         <f t="shared" si="10"/>
-        <v>15.050182254616306</v>
+        <v>1505.0182254616304</v>
       </c>
       <c r="S47" s="34">
-        <f t="shared" si="16"/>
-        <v>-5.9403908886824439</v>
+        <f t="shared" si="15"/>
+        <v>-5.9403908886824563</v>
       </c>
       <c r="T47" s="32"/>
       <c r="U47" s="11">
@@ -12453,7 +15186,7 @@
         <v>64362364994.375397</v>
       </c>
       <c r="AH47" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>27.171590089942871</v>
       </c>
       <c r="AI47" s="29">
@@ -12482,7 +15215,7 @@
         <v>1965.3094343747164</v>
       </c>
       <c r="G48" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>8.7909344767513637</v>
       </c>
       <c r="H48" s="30"/>
@@ -12503,25 +15236,25 @@
         <f t="shared" si="9"/>
         <v>93.62</v>
       </c>
-      <c r="O48" s="34">
+      <c r="O48" s="36">
+        <f t="shared" si="4"/>
+        <v>515240363.44739997</v>
+      </c>
+      <c r="P48" s="34">
         <f t="shared" si="11"/>
-        <v>51524036344.740005</v>
-      </c>
-      <c r="P48" s="34">
+        <v>5394.2750920018307</v>
+      </c>
+      <c r="Q48" s="34">
         <f t="shared" si="12"/>
-        <v>53.942750920018298</v>
-      </c>
-      <c r="Q48" s="34">
-        <f t="shared" si="13"/>
-        <v>4.4602841339163337</v>
+        <v>4.4602841339163648</v>
       </c>
       <c r="R48" s="35">
         <f t="shared" si="10"/>
-        <v>16.84395804446174</v>
+        <v>1684.3958044461742</v>
       </c>
       <c r="S48" s="34">
-        <f t="shared" si="16"/>
-        <v>11.918631678332222</v>
+        <f t="shared" si="15"/>
+        <v>11.918631678332252</v>
       </c>
       <c r="T48" s="32"/>
       <c r="U48" s="11">
@@ -12560,7 +15293,7 @@
         <v>44727277562.880997</v>
       </c>
       <c r="AH48" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-30.507094376053928</v>
       </c>
       <c r="AI48" s="29">
@@ -12589,7 +15322,7 @@
         <v>2098.2112447612194</v>
       </c>
       <c r="G49" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.7623860172831822</v>
       </c>
       <c r="H49" s="30"/>
@@ -12610,25 +15343,25 @@
         <f t="shared" si="9"/>
         <v>95.177999999999997</v>
       </c>
-      <c r="O49" s="34">
+      <c r="O49" s="36">
+        <f t="shared" si="4"/>
+        <v>541711171.09325993</v>
+      </c>
+      <c r="P49" s="34">
         <f t="shared" si="11"/>
-        <v>54171117109.325996</v>
-      </c>
-      <c r="P49" s="34">
+        <v>5521.0953208257888</v>
+      </c>
+      <c r="Q49" s="34">
         <f t="shared" si="12"/>
-        <v>55.210953208257884</v>
-      </c>
-      <c r="Q49" s="34">
-        <f t="shared" si="13"/>
-        <v>2.3510152274583986</v>
+        <v>2.3510152274583902</v>
       </c>
       <c r="R49" s="35">
         <f t="shared" si="10"/>
-        <v>17.373860892845848</v>
+        <v>1737.3860892845851</v>
       </c>
       <c r="S49" s="34">
-        <f t="shared" si="16"/>
-        <v>3.1459520795846361</v>
+        <f t="shared" si="15"/>
+        <v>3.1459520795846401</v>
       </c>
       <c r="T49" s="32"/>
       <c r="U49" s="11">
@@ -12667,7 +15400,7 @@
         <v>49940258404.2659</v>
       </c>
       <c r="AH49" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>11.655037206447675</v>
       </c>
       <c r="AI49" s="29">
@@ -12696,7 +15429,7 @@
         <v>2229.7149122303699</v>
       </c>
       <c r="G50" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.2674179159742271</v>
       </c>
       <c r="H50" s="30"/>
@@ -12717,25 +15450,25 @@
         <f t="shared" si="9"/>
         <v>95.828000000000003</v>
       </c>
-      <c r="O50" s="34">
+      <c r="O50" s="36">
+        <f t="shared" si="4"/>
+        <v>564893462.45112002</v>
+      </c>
+      <c r="P50" s="34">
         <f t="shared" si="11"/>
-        <v>56489346245.112</v>
-      </c>
-      <c r="P50" s="34">
+        <v>5676.2654131508198</v>
+      </c>
+      <c r="Q50" s="34">
         <f t="shared" si="12"/>
-        <v>56.762654131508199</v>
-      </c>
-      <c r="Q50" s="34">
-        <f t="shared" si="13"/>
-        <v>2.8104947172298198</v>
+        <v>2.8104947172298091</v>
       </c>
       <c r="R50" s="35">
         <f t="shared" si="10"/>
-        <v>17.869267764506674</v>
+        <v>1786.9267764506671</v>
       </c>
       <c r="S50" s="34">
-        <f t="shared" si="16"/>
-        <v>2.851449512093327</v>
+        <f t="shared" si="15"/>
+        <v>2.851449512093295</v>
       </c>
       <c r="T50" s="32"/>
       <c r="U50" s="11">
@@ -12774,7 +15507,7 @@
         <v>28086193530.3979</v>
       </c>
       <c r="AH50" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-43.760416089479477</v>
       </c>
       <c r="AI50" s="29">
@@ -12803,7 +15536,7 @@
         <v>2366.8328910323048</v>
       </c>
       <c r="G51" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.1495744612828842</v>
       </c>
       <c r="H51" s="30"/>
@@ -12824,25 +15557,25 @@
         <f t="shared" si="9"/>
         <v>95.826999999999998</v>
       </c>
-      <c r="O51" s="34">
+      <c r="O51" s="36">
+        <f t="shared" si="4"/>
+        <v>583108066.40734994</v>
+      </c>
+      <c r="P51" s="34">
         <f t="shared" si="11"/>
-        <v>58310806640.735001</v>
-      </c>
-      <c r="P51" s="34">
+        <v>5889.3415316188593</v>
+      </c>
+      <c r="Q51" s="34">
         <f t="shared" si="12"/>
-        <v>58.893415316188587</v>
-      </c>
-      <c r="Q51" s="34">
-        <f t="shared" si="13"/>
-        <v>3.7538082340967045</v>
+        <v>3.7538082340967178</v>
       </c>
       <c r="R51" s="35">
         <f t="shared" si="10"/>
-        <v>18.420700746666533</v>
+        <v>1842.0700746666532</v>
       </c>
       <c r="S51" s="34">
-        <f t="shared" si="16"/>
-        <v>3.0859293700615886</v>
+        <f t="shared" si="15"/>
+        <v>3.0859293700615971</v>
       </c>
       <c r="T51" s="32"/>
       <c r="U51" s="11">
@@ -12881,7 +15614,7 @@
         <v>27139853378.140202</v>
       </c>
       <c r="AH51" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-3.3694140547506621</v>
       </c>
       <c r="AI51" s="29">
@@ -12910,7 +15643,7 @@
         <v>2523.4360185137643</v>
       </c>
       <c r="G52" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>6.6165688365584767</v>
       </c>
       <c r="H52" s="30"/>
@@ -12931,25 +15664,25 @@
         <f t="shared" si="9"/>
         <v>95.781000000000006</v>
       </c>
-      <c r="O52" s="34">
+      <c r="O52" s="36">
+        <f t="shared" si="4"/>
+        <v>591567723.0741601</v>
+      </c>
+      <c r="P52" s="34">
         <f t="shared" si="11"/>
-        <v>59156772307.416</v>
-      </c>
-      <c r="P52" s="34">
+        <v>6244.3754923770211</v>
+      </c>
+      <c r="Q52" s="34">
         <f t="shared" si="12"/>
-        <v>62.443754923770214</v>
-      </c>
-      <c r="Q52" s="34">
-        <f t="shared" si="13"/>
-        <v>6.0284152116505147</v>
+        <v>6.0284152116504996</v>
       </c>
       <c r="R52" s="35">
         <f t="shared" si="10"/>
-        <v>19.443319943424203</v>
+        <v>1944.3319943424201</v>
       </c>
       <c r="S52" s="34">
-        <f t="shared" si="16"/>
-        <v>5.5514673997552819</v>
+        <f t="shared" si="15"/>
+        <v>5.5514673997552739</v>
       </c>
       <c r="T52" s="32"/>
       <c r="U52" s="11">
@@ -12988,7 +15721,7 @@
         <v>39097233086.213303</v>
       </c>
       <c r="AH52" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>44.058379908950336</v>
       </c>
       <c r="AI52" s="29">
